--- a/ONCHO/Entomological survey Survey/Nigeria/2025/enugu-kaduna/ng_oncho_2505_2_river_inspection_enu_kad.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2025/enugu-kaduna/ng_oncho_2505_2_river_inspection_enu_kad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\enugu-kaduna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\enugu-kaduna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB70F37-9860-4055-B389-3ACA48D6F0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC079B97-8EDF-4F42-B4CB-162786BA324D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="371">
   <si>
     <t>type</t>
   </si>
@@ -532,9 +532,6 @@
     <t>community = ${r_community}</t>
   </si>
   <si>
-    <t>ng_oncho_2505_2_river_inspection_enu_kad</t>
-  </si>
-  <si>
     <t>ENUGU</t>
   </si>
   <si>
@@ -1147,7 +1144,16 @@
     <t>KAD_JEM_M_001</t>
   </si>
   <si>
-    <t>(Enugu Kaduna) 2. River inspection Form</t>
+    <t>(Enugu Kaduna) 2. River inspection Form V2</t>
+  </si>
+  <si>
+    <t>ng_oncho_2505_2_river_inspection_enu_kad_v2</t>
+  </si>
+  <si>
+    <t>UGWOGO</t>
+  </si>
+  <si>
+    <t>ENU_ENE_M_096</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1348,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2528,7 +2544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.125" customWidth="1"/>
@@ -2840,10 +2856,10 @@
         <v>107</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2851,14 +2867,13 @@
         <v>107</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
     </row>
@@ -2867,13 +2882,13 @@
         <v>106</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2881,13 +2896,13 @@
         <v>106</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2895,13 +2910,13 @@
         <v>106</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2909,13 +2924,13 @@
         <v>106</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2923,114 +2938,115 @@
         <v>106</v>
       </c>
       <c r="B39" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D39" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C40" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D45" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D46" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>106</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="D40" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>106</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="D41" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>106</v>
-      </c>
-      <c r="B42" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="D42" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>106</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D43" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>106</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="D44" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>106</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D45" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>106</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D46" t="s">
-        <v>165</v>
-      </c>
-    </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="20"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
     </row>
@@ -3039,13 +3055,13 @@
         <v>155</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3053,13 +3069,13 @@
         <v>155</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E49" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3067,13 +3083,13 @@
         <v>155</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3081,13 +3097,13 @@
         <v>155</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3095,13 +3111,13 @@
         <v>155</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>182</v>
+        <v>369</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>182</v>
+        <v>369</v>
       </c>
       <c r="E52" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3109,13 +3125,13 @@
         <v>155</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3123,13 +3139,13 @@
         <v>155</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E54" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3137,13 +3153,13 @@
         <v>155</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3151,237 +3167,237 @@
         <v>155</v>
       </c>
       <c r="B56" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>155</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C58" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="E56" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B57" s="21" t="s">
+      <c r="E58" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C59" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="E57" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B58" s="21" t="s">
+      <c r="E59" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C60" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="E58" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B59" s="21" t="s">
+      <c r="E60" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C61" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="E59" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B60" s="21" t="s">
+      <c r="E61" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C62" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="E60" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B61" s="21" t="s">
+      <c r="E62" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C63" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="E61" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B62" s="21" t="s">
+      <c r="E63" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>155</v>
+      </c>
+      <c r="B64" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="C62" s="21" t="s">
+      <c r="C64" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="E62" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B63" s="21" t="s">
+      <c r="E64" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>155</v>
+      </c>
+      <c r="B65" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C63" s="21" t="s">
+      <c r="C65" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="E63" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B64" s="21" t="s">
+      <c r="E65" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="C66" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="E64" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B65" s="21" t="s">
+      <c r="E66" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C67" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E65" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B66" s="21" t="s">
+      <c r="E67" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>155</v>
+      </c>
+      <c r="B68" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C68" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="E66" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B67" s="21" t="s">
+      <c r="E68" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C69" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="E67" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" s="21" t="s">
+      <c r="E69" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="C68" s="21" t="s">
+      <c r="C70" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="E68" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B69" s="21" t="s">
+      <c r="E70" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>155</v>
+      </c>
+      <c r="B71" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C71" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="E69" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B70" s="21" t="s">
+      <c r="E71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+      <c r="B72" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C72" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="E70" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B71" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="E71" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B72" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>202</v>
-      </c>
       <c r="E72" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3389,13 +3405,13 @@
         <v>155</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3403,13 +3419,13 @@
         <v>155</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E74" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3417,13 +3433,13 @@
         <v>155</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E75" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3431,13 +3447,13 @@
         <v>155</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E76" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3445,13 +3461,13 @@
         <v>155</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E77" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3459,13 +3475,13 @@
         <v>155</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E78" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3473,13 +3489,13 @@
         <v>155</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E79" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3487,13 +3503,13 @@
         <v>155</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E80" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3501,13 +3517,13 @@
         <v>155</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3515,13 +3531,13 @@
         <v>155</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E82" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3529,13 +3545,13 @@
         <v>155</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E83" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3543,13 +3559,13 @@
         <v>155</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E84" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3557,13 +3573,13 @@
         <v>155</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E85" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3571,41 +3587,41 @@
         <v>155</v>
       </c>
       <c r="B86" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="E86" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="E87" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>155</v>
+      </c>
+      <c r="B88" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="C86" s="21" t="s">
+      <c r="C88" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="E86" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>155</v>
-      </c>
-      <c r="B87" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="E87" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>155</v>
-      </c>
-      <c r="B88" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="C88" s="21" t="s">
-        <v>218</v>
-      </c>
       <c r="E88" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3613,13 +3629,13 @@
         <v>155</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E89" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3627,13 +3643,13 @@
         <v>155</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E90" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3641,13 +3657,13 @@
         <v>155</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E91" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3655,13 +3671,13 @@
         <v>155</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E92" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3669,13 +3685,13 @@
         <v>155</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -3683,13 +3699,13 @@
         <v>155</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E94" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3697,13 +3713,13 @@
         <v>155</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E95" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3711,13 +3727,13 @@
         <v>155</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E96" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -3725,13 +3741,13 @@
         <v>155</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E97" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -3739,13 +3755,13 @@
         <v>155</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E98" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -3753,13 +3769,13 @@
         <v>155</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E99" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -3767,13 +3783,13 @@
         <v>155</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E100" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -3781,13 +3797,13 @@
         <v>155</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E101" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -3795,13 +3811,13 @@
         <v>155</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E102" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -3809,13 +3825,13 @@
         <v>155</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E103" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -3823,13 +3839,13 @@
         <v>155</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E104" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -3837,13 +3853,13 @@
         <v>155</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E105" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -3851,13 +3867,13 @@
         <v>155</v>
       </c>
       <c r="B106" s="21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E106" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -3865,536 +3881,535 @@
         <v>155</v>
       </c>
       <c r="B107" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C107" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="E107" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>155</v>
+      </c>
+      <c r="B108" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="C108" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="E108" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>155</v>
+      </c>
+      <c r="B109" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="C107" s="21" t="s">
+      <c r="C109" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E109" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>155</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="E110" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>155</v>
+      </c>
+      <c r="B111" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E111" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>155</v>
+      </c>
+      <c r="B112" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C112" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="E112" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>155</v>
+      </c>
+      <c r="B113" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="C113" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E113" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>155</v>
+      </c>
+      <c r="B114" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="E114" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B108" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="C108" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="E108" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>155</v>
+      </c>
+      <c r="B115" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="C115" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E115" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B109" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="C109" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="E109" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>155</v>
+      </c>
+      <c r="B116" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="C116" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="E116" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B110" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="C110" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E110" t="s">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>155</v>
+      </c>
+      <c r="B117" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C117" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="E117" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B111" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="C111" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="E111" t="s">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>155</v>
+      </c>
+      <c r="B118" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C118" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="E118" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B112" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="C112" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="E112" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>155</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C119" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E119" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B113" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="C113" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="E113" t="s">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>155</v>
+      </c>
+      <c r="B120" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E120" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>155</v>
+      </c>
+      <c r="B121" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="C121" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="E121" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>155</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E122" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B114" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="C114" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="E114" t="s">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>155</v>
+      </c>
+      <c r="B123" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="C123" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E123" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B115" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="C115" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="E115" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>155</v>
+      </c>
+      <c r="B124" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C124" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="E124" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B116" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="C116" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="E116" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>155</v>
+      </c>
+      <c r="B125" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="C125" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="E125" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B117" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="C117" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="E117" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>155</v>
+      </c>
+      <c r="B126" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="C126" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="E126" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B118" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="C118" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="E118" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>155</v>
+      </c>
+      <c r="B127" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="C127" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="E127" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B119" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="C119" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="E119" t="s">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>155</v>
+      </c>
+      <c r="B128" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C128" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="E128" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B120" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="C120" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="E120" t="s">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>155</v>
+      </c>
+      <c r="B129" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="C129" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="E129" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B121" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="C121" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="E121" t="s">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>155</v>
+      </c>
+      <c r="B130" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C130" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="E130" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>155</v>
+      </c>
+      <c r="B131" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="E131" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>155</v>
+      </c>
+      <c r="B132" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C132" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E132" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>155</v>
+      </c>
+      <c r="B133" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C133" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="E133" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>155</v>
+      </c>
+      <c r="B134" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C134" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="E134" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>155</v>
+      </c>
+      <c r="B135" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C135" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="E135" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>155</v>
+      </c>
+      <c r="B136" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C136" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E136" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>155</v>
+      </c>
+      <c r="B137" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C137" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="E137" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B122" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="C122" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="E122" t="s">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>155</v>
+      </c>
+      <c r="B138" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="C138" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="E138" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B123" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="C123" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="E123" t="s">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>155</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="C139" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="E139" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B124" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="C124" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="E124" t="s">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>155</v>
+      </c>
+      <c r="B140" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="C140" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="E140" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B125" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="C125" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="E125" t="s">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>155</v>
+      </c>
+      <c r="B141" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C141" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="E141" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B126" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="C126" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="E126" t="s">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>155</v>
+      </c>
+      <c r="B142" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="C142" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="E142" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B127" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="C127" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="E127" t="s">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>155</v>
+      </c>
+      <c r="B143" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="C143" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E143" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B128" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="C128" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="E128" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B129" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C129" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="E129" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B130" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="C130" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="E130" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B131" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="C131" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="E131" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B132" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="C132" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="E132" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B133" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="C133" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="E133" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B134" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="C134" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="E134" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B135" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="C135" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="E135" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B136" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="C136" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="E136" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B137" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="C137" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="E137" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B138" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="C138" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="E138" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B139" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="C139" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="E139" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B140" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="C140" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="E140" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B141" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="C141" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="E141" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B142" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="C142" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="E142" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="20"/>
-      <c r="B143" s="21"/>
-      <c r="C143" s="21"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B144" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="C144" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="F144" t="s">
-        <v>184</v>
-      </c>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B144" s="21"/>
+      <c r="C144" s="21"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="20" t="s">
         <v>38</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="F145" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4402,13 +4417,13 @@
         <v>38</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="F146" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4416,13 +4431,13 @@
         <v>38</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="C147" s="21" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="F147" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4430,13 +4445,13 @@
         <v>38</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="C148" s="21" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="F148" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4444,13 +4459,13 @@
         <v>38</v>
       </c>
       <c r="B149" s="21" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="C149" s="21" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="F149" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4458,13 +4473,13 @@
         <v>38</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="C150" s="21" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="F150" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4472,13 +4487,13 @@
         <v>38</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>279</v>
+        <v>370</v>
       </c>
       <c r="C151" s="21" t="s">
-        <v>279</v>
+        <v>370</v>
       </c>
       <c r="F151" t="s">
-        <v>198</v>
+        <v>369</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4500,13 +4515,13 @@
         <v>38</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C153" s="21" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F153" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4514,13 +4529,13 @@
         <v>38</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C154" s="21" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F154" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4528,13 +4543,13 @@
         <v>38</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C155" s="21" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F155" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4542,13 +4557,13 @@
         <v>38</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="C156" s="21" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="F156" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4556,13 +4571,13 @@
         <v>38</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="F157" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4570,13 +4585,13 @@
         <v>38</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="F158" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4584,13 +4599,13 @@
         <v>38</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="F159" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4598,13 +4613,13 @@
         <v>38</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="F160" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4612,13 +4627,13 @@
         <v>38</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="F161" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4626,13 +4641,13 @@
         <v>38</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="F162" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4640,13 +4655,13 @@
         <v>38</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="F163" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4654,13 +4669,13 @@
         <v>38</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>253</v>
+        <v>183</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4668,1057 +4683,1082 @@
         <v>38</v>
       </c>
       <c r="B165" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="C165" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="F165" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B166" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="C166" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="F166" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B167" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C167" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="F167" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B168" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C168" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="F168" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B169" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="C169" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="F169" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B170" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="C170" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="F170" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B171" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="C171" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="F171" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="C172" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="F172" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B173" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C173" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="F173" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B174" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="C174" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="F174" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B175" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C175" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F175" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B176" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="C176" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="F176" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B177" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C177" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="F177" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B178" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="C178" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F178" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B179" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C179" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="F179" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B180" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="C180" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="F180" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B181" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="C181" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="F181" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B182" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="C182" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="F182" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B183" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="C183" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="F183" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B184" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C184" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="F184" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B185" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C185" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="F185" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B186" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="C186" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="F186" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B187" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C187" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="F187" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B188" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C188" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="F188" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B189" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C189" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="F189" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B190" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="C190" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="F190" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B191" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="C191" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="F191" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B192" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C192" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="F192" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B193" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C193" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="F193" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B194" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="C194" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="F194" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B195" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="C195" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="F195" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B196" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="C196" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="F196" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B197" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C197" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="F197" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B198" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="C198" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="F198" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B199" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="C199" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="F199" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B200" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="C200" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="F200" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B201" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C201" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="F201" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B202" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="C202" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="F202" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B203" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="C203" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="F203" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B204" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="C204" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="F204" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B205" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="C205" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F205" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B206" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="C206" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="F206" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B207" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="C207" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="F207" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B208" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="C208" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="F208" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B209" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="C209" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="F209" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B210" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C210" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="F210" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B211" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="C211" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="F211" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B212" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C212" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="F212" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B213" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C213" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="F213" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B214" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="C214" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="F214" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B215" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="C215" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="F215" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B216" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C216" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="F216" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B217" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="C217" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="F217" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B218" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C218" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="F218" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B219" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="C219" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="F219" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B220" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="C220" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="F220" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B221" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C221" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="F221" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B222" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="C222" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="F222" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B223" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C223" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="F223" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B224" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C224" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="F224" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B225" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C225" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="F225" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B226" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C226" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="F226" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B227" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C227" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="F227" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B228" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C228" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="F228" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B229" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C229" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="F229" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B230" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C230" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="F230" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B231" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C231" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="F231" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B232" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="C232" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="F232" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B233" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="C233" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="F233" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B234" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="C234" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="F234" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B235" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="C235" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="F235" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B236" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="C236" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="F236" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B237" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C237" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="F237" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B238" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="C238" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="F238" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B239" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C239" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="F239" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B240" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="C165" s="21" t="s">
+      <c r="C240" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="F165" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>38</v>
-      </c>
-      <c r="B166" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="C166" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="F166" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>38</v>
-      </c>
-      <c r="B167" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="C167" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="F167" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>38</v>
-      </c>
-      <c r="B168" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="C168" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="F168" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>38</v>
-      </c>
-      <c r="B169" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C169" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="F169" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>38</v>
-      </c>
-      <c r="B170" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="F170" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>38</v>
-      </c>
-      <c r="B171" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="C171" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="F171" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>38</v>
-      </c>
-      <c r="B172" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="C172" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="F172" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>38</v>
-      </c>
-      <c r="B173" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="C173" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="F173" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>38</v>
-      </c>
-      <c r="B174" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="C174" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="F174" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>38</v>
-      </c>
-      <c r="B175" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="C175" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="F175" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>38</v>
-      </c>
-      <c r="B176" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="C176" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="F176" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>38</v>
-      </c>
-      <c r="B177" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="C177" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="F177" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>38</v>
-      </c>
-      <c r="B178" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="C178" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="F178" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>38</v>
-      </c>
-      <c r="B179" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="C179" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="F179" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>38</v>
-      </c>
-      <c r="B180" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="C180" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="F180" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>38</v>
-      </c>
-      <c r="B181" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="C181" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="F181" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>38</v>
-      </c>
-      <c r="B182" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="C182" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="F182" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>38</v>
-      </c>
-      <c r="B183" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="C183" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="F183" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>38</v>
-      </c>
-      <c r="B184" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="C184" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="F184" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>38</v>
-      </c>
-      <c r="B185" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="C185" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="F185" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>38</v>
-      </c>
-      <c r="B186" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="C186" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="F186" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>38</v>
-      </c>
-      <c r="B187" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="C187" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="F187" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>38</v>
-      </c>
-      <c r="B188" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="C188" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="F188" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>38</v>
-      </c>
-      <c r="B189" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="C189" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="F189" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>38</v>
-      </c>
-      <c r="B190" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C190" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="F190" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>38</v>
-      </c>
-      <c r="B191" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="C191" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="F191" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>38</v>
-      </c>
-      <c r="B192" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="C192" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="F192" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>38</v>
-      </c>
-      <c r="B193" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="C193" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="F193" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>38</v>
-      </c>
-      <c r="B194" s="18" t="s">
-        <v>322</v>
-      </c>
-      <c r="C194" s="18" t="s">
-        <v>322</v>
-      </c>
-      <c r="F194" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>38</v>
-      </c>
-      <c r="B195" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C195" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="F195" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>38</v>
-      </c>
-      <c r="B196" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="C196" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F196" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>38</v>
-      </c>
-      <c r="B197" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="C197" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="F197" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>38</v>
-      </c>
-      <c r="B198" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="C198" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="F198" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>38</v>
-      </c>
-      <c r="B199" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="C199" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="F199" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>38</v>
-      </c>
-      <c r="B200" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="C200" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="F200" t="s">
+      <c r="F240" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B241" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="C241" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="F241" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>38</v>
-      </c>
-      <c r="B201" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="C201" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="F201" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>38</v>
-      </c>
-      <c r="B202" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="C202" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F202" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>38</v>
-      </c>
-      <c r="B203" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="C203" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="F203" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>38</v>
-      </c>
-      <c r="B204" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="C204" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="F204" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>38</v>
-      </c>
-      <c r="B205" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="C205" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="F205" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>38</v>
-      </c>
-      <c r="B206" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="C206" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="F206" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>38</v>
-      </c>
-      <c r="B207" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="C207" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="F207" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>38</v>
-      </c>
-      <c r="B208" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="C208" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="F208" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>38</v>
-      </c>
-      <c r="B209" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="C209" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="F209" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>38</v>
-      </c>
-      <c r="B210" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="C210" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="F210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>38</v>
-      </c>
-      <c r="B211" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C211" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="F211" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>38</v>
-      </c>
-      <c r="B212" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="C212" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="F212" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>38</v>
-      </c>
-      <c r="B213" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="C213" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="F213" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>38</v>
-      </c>
-      <c r="B214" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="C214" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="F214" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>38</v>
-      </c>
-      <c r="B215" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="C215" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="F215" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>38</v>
-      </c>
-      <c r="B216" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="C216" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="F216" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>38</v>
-      </c>
-      <c r="B217" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="C217" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="F217" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>38</v>
-      </c>
-      <c r="B218" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="C218" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="F218" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>38</v>
-      </c>
-      <c r="B219" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="C219" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="F219" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>38</v>
-      </c>
-      <c r="B220" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="C220" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="F220" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>38</v>
-      </c>
-      <c r="B221" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="C221" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="F221" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>38</v>
-      </c>
-      <c r="B222" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="C222" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="F222" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>38</v>
-      </c>
-      <c r="B223" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="C223" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="F223" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>38</v>
-      </c>
-      <c r="B224" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C224" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="F224" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>38</v>
-      </c>
-      <c r="B225" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C225" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="F225" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>38</v>
-      </c>
-      <c r="B226" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="C226" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="F226" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>38</v>
-      </c>
-      <c r="B227" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="C227" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="F227" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>38</v>
-      </c>
-      <c r="B228" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="C228" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="F228" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>38</v>
-      </c>
-      <c r="B229" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="C229" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="F229" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>38</v>
-      </c>
-      <c r="B230" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="C230" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="F230" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>38</v>
-      </c>
-      <c r="B231" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="C231" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="F231" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>38</v>
-      </c>
-      <c r="B232" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="C232" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="F232" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>38</v>
-      </c>
-      <c r="B233" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="C233" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="F233" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>38</v>
-      </c>
-      <c r="B234" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="C234" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="F234" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>38</v>
-      </c>
-      <c r="B235" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="C235" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="F235" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>38</v>
-      </c>
-      <c r="B236" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C236" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="F236" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>38</v>
-      </c>
-      <c r="B237" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="C237" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="F237" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>38</v>
-      </c>
-      <c r="B238" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="C238" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="F238" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>38</v>
-      </c>
-      <c r="B239" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="C239" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="F239" t="s">
-        <v>213</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C57">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C108:C154">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="C145">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5747,12 +5787,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>368</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>21</v>
